--- a/CRC-HL2_EmitaCityRP.Emita_2025/Arma HL2-Outbreak Loot Table.xlsx
+++ b/CRC-HL2_EmitaCityRP.Emita_2025/Arma HL2-Outbreak Loot Table.xlsx
@@ -28,7 +28,7 @@
     <t>Secondary Magazine</t>
   </si>
   <si>
-    <t>Compatible Attatchments</t>
+    <t xml:space="preserve">Compatible Attachments </t>
   </si>
   <si>
     <t>HL_SniperAssasin</t>
